--- a/code/因子回测统计结果.xlsx
+++ b/code/因子回测统计结果.xlsx
@@ -870,7 +870,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>持有期</t>
+          <t>持有期(天)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>持有期</t>
+          <t>持有期(天)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -18283,7 +18283,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>持有期</t>
+          <t>持有期(天)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -18477,7 +18477,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>持有期</t>
+          <t>持有期(天)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
